--- a/accuracy_time/results.xlsx
+++ b/accuracy_time/results.xlsx
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="results" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -33,13 +33,13 @@
     <t>Total Area</t>
   </si>
   <si>
+    <t>Elapsed Time (us)</t>
+  </si>
+  <si>
     <t>1- COS(b)</t>
   </si>
   <si>
-    <t>ERROR</t>
-  </si>
-  <si>
-    <t>Elapsed Time (us)</t>
+    <t>error_area</t>
   </si>
 </sst>
 </file>
@@ -523,8 +523,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -601,18 +602,18 @@
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
-        <c:scatterStyle val="smoothMarker"/>
+        <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>results!$E$15</c:f>
+              <c:f>results!$F$13</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Elapsed Time (us)</c:v>
+                  <c:v>error_area</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -643,29 +644,26 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>results!$D$16:$D$22</c:f>
+              <c:f>results!$E$14:$E$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>10</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>100000</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1000000</c:v>
-                </c:pt>
-                <c:pt idx="6">
                   <c:v>10000000</c:v>
                 </c:pt>
               </c:numCache>
@@ -673,38 +671,35 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>results!$E$16:$E$22</c:f>
+              <c:f>results!$F$14:$F$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>1.27774299999994E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>9.7430000000064965E-6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>5.2256999999999998E-5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>8.2256999999974489E-5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>2.3257000000054262E-5</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>5000000</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>65000000</c:v>
+                <c:pt idx="5" formatCode="0.00E+00">
+                  <c:v>6.7430000000312501E-6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4AB2-4046-ABDC-665DE08996D5}"/>
+              <c16:uniqueId val="{00000000-E663-4703-BCA3-B0754834FA92}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -716,11 +711,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1464067583"/>
-        <c:axId val="1464069247"/>
+        <c:axId val="708708800"/>
+        <c:axId val="708715456"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1464067583"/>
+        <c:axId val="708708800"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -848,15 +843,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1464069247"/>
+        <c:crossAx val="708715456"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1464069247"/>
+        <c:axId val="708715456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -909,7 +903,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>Elapsed Time (us)</a:t>
+                  <a:t>error_area</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -981,42 +975,9 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1464067583"/>
+        <c:crossAx val="708708800"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
-        <c:dispUnits>
-          <c:builtInUnit val="millions"/>
-          <c:dispUnitsLbl>
-            <c:layout/>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-          </c:dispUnitsLbl>
-        </c:dispUnits>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -1120,11 +1081,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>results!$E$28</c:f>
+              <c:f>results!$F$30</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>ERROR</c:v>
+                  <c:v>Elapsed Time (us)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1155,29 +1116,26 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>results!$D$29:$D$35</c:f>
+              <c:f>results!$E$31:$E$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>10</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>100</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10000</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>100000</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1000000</c:v>
-                </c:pt>
-                <c:pt idx="6">
                   <c:v>10000000</c:v>
                 </c:pt>
               </c:numCache>
@@ -1185,30 +1143,27 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>results!$E$29:$E$35</c:f>
+              <c:f>results!$F$31:$F$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2.9492999999999998E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.3060000000000003E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.6512E-2</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.8587E-2</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.8541999999999997E-2</c:v>
+                  <c:v>5000000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.8465999999999997E-2</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>5.8428000000000001E-2</c:v>
+                  <c:v>67000000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1216,7 +1171,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F9DF-49F5-A4ED-591CB187D72B}"/>
+              <c16:uniqueId val="{00000000-A4BA-4A0A-BC5D-FB509BC4F35F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1228,11 +1183,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1472678511"/>
-        <c:axId val="1472683087"/>
+        <c:axId val="1007394528"/>
+        <c:axId val="1007397856"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1472678511"/>
+        <c:axId val="1007394528"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -1360,12 +1315,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1472683087"/>
+        <c:crossAx val="1007397856"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1472683087"/>
+        <c:axId val="1007397856"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1420,7 +1375,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>ERROR</a:t>
+                  <a:t>Elapsed Time (us)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -1492,9 +1447,42 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1472678511"/>
+        <c:crossAx val="1007394528"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
+        <c:dispUnits>
+          <c:builtInUnit val="millions"/>
+          <c:dispUnitsLbl>
+            <c:layout/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+          </c:dispUnitsLbl>
+        </c:dispUnits>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -2689,16 +2677,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>53340</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>118110</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>125730</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>358140</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>118110</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>125730</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2719,16 +2707,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>179070</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>335280</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>179070</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3013,8 +3001,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -3030,13 +3021,13 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
         <v>6</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -3047,10 +3038,10 @@
         <v>330</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D2">
-        <v>0.65151499999999996</v>
+        <v>0.62329999999999997</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -3059,7 +3050,8 @@
         <v>0.62202225700000002</v>
       </c>
       <c r="G2">
-        <v>2.9492999999999998E-2</v>
+        <f t="shared" ref="G2:G7" si="0">ABS(D2-F2)</f>
+        <v>1.2777429999999423E-3</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -3070,10 +3062,10 @@
         <v>330</v>
       </c>
       <c r="C3">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="D3">
-        <v>0.67508199999999996</v>
+        <v>0.62203200000000003</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -3082,7 +3074,8 @@
         <v>0.62202225700000002</v>
       </c>
       <c r="G3">
-        <v>5.3060000000000003E-2</v>
+        <f t="shared" si="0"/>
+        <v>9.7430000000064965E-6</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -3093,19 +3086,20 @@
         <v>330</v>
       </c>
       <c r="C4">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="D4">
-        <v>0.67853399999999997</v>
+        <v>0.62197000000000002</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="F4">
         <v>0.62202225700000002</v>
       </c>
       <c r="G4">
-        <v>5.6512E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.2256999999999998E-5</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -3116,19 +3110,20 @@
         <v>330</v>
       </c>
       <c r="C5">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="D5">
-        <v>0.68060900000000002</v>
+        <v>0.62194000000000005</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="F5">
         <v>0.62202225700000002</v>
       </c>
       <c r="G5">
-        <v>5.8587E-2</v>
+        <f t="shared" si="0"/>
+        <v>8.2256999999974489E-5</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -3139,19 +3134,20 @@
         <v>330</v>
       </c>
       <c r="C6">
-        <v>100000</v>
+        <v>1000000</v>
       </c>
       <c r="D6">
-        <v>0.68056399999999995</v>
+        <v>0.62199899999999997</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="F6">
         <v>0.62202225700000002</v>
       </c>
       <c r="G6">
-        <v>5.8541999999999997E-2</v>
+        <f t="shared" si="0"/>
+        <v>2.3257000000054262E-5</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -3162,170 +3158,132 @@
         <v>330</v>
       </c>
       <c r="C7">
-        <v>1000000</v>
+        <v>10000000</v>
       </c>
       <c r="D7">
-        <v>0.68048799999999998</v>
+        <v>0.62202900000000005</v>
       </c>
       <c r="E7">
-        <v>5000000</v>
+        <v>67000000</v>
       </c>
       <c r="F7">
         <v>0.62202225700000002</v>
       </c>
       <c r="G7">
-        <v>5.8465999999999997E-2</v>
+        <f t="shared" si="0"/>
+        <v>6.7430000000312518E-6</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>330</v>
-      </c>
-      <c r="C8">
-        <v>10000000</v>
-      </c>
-      <c r="D8">
-        <v>0.68045</v>
-      </c>
-      <c r="E8">
-        <v>65000000</v>
-      </c>
-      <c r="F8">
-        <v>0.62202225700000002</v>
-      </c>
-      <c r="G8">
-        <v>5.8428000000000001E-2</v>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E13" t="s">
+        <v>2</v>
+      </c>
+      <c r="F13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E14">
+        <v>100</v>
+      </c>
+      <c r="F14">
+        <v>1.27774299999994E-3</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="D15" t="s">
-        <v>2</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
+      <c r="E15">
+        <v>1000</v>
+      </c>
+      <c r="F15">
+        <v>9.7430000000064965E-6</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="D16">
-        <v>10</v>
-      </c>
       <c r="E16">
+        <v>10000</v>
+      </c>
+      <c r="F16">
+        <v>5.2256999999999998E-5</v>
+      </c>
+    </row>
+    <row r="17" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E17">
+        <v>100000</v>
+      </c>
+      <c r="F17">
+        <v>8.2256999999974489E-5</v>
+      </c>
+    </row>
+    <row r="18" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E18">
+        <v>1000000</v>
+      </c>
+      <c r="F18">
+        <v>2.3257000000054262E-5</v>
+      </c>
+    </row>
+    <row r="19" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E19">
+        <v>10000000</v>
+      </c>
+      <c r="F19" s="1">
+        <v>6.7430000000312501E-6</v>
+      </c>
+    </row>
+    <row r="30" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E30" t="s">
+        <v>2</v>
+      </c>
+      <c r="F30" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E31">
+        <v>100</v>
+      </c>
+      <c r="F31">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D17">
-        <v>100</v>
-      </c>
-      <c r="E17">
+    <row r="32" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E32">
+        <v>1000</v>
+      </c>
+      <c r="F32">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D18">
-        <v>1000</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
+    <row r="33" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E33">
+        <v>10000</v>
+      </c>
+      <c r="F33">
+        <v>1000000</v>
       </c>
     </row>
-    <row r="19" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D19">
-        <v>10000</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
+    <row r="34" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E34">
+        <v>100000</v>
+      </c>
+      <c r="F34">
+        <v>1000000</v>
       </c>
     </row>
-    <row r="20" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D20">
-        <v>100000</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
+    <row r="35" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E35">
+        <v>1000000</v>
+      </c>
+      <c r="F35">
+        <v>5000000</v>
       </c>
     </row>
-    <row r="21" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D21">
-        <v>1000000</v>
-      </c>
-      <c r="E21">
-        <v>5000000</v>
-      </c>
-    </row>
-    <row r="22" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D22">
+    <row r="36" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E36">
         <v>10000000</v>
       </c>
-      <c r="E22">
-        <v>65000000</v>
-      </c>
-    </row>
-    <row r="28" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D28" t="s">
-        <v>2</v>
-      </c>
-      <c r="E28" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D29">
-        <v>10</v>
-      </c>
-      <c r="E29">
-        <v>2.9492999999999998E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D30">
-        <v>100</v>
-      </c>
-      <c r="E30">
-        <v>5.3060000000000003E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D31">
-        <v>1000</v>
-      </c>
-      <c r="E31">
-        <v>5.6512E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D32">
-        <v>10000</v>
-      </c>
-      <c r="E32">
-        <v>5.8587E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D33">
-        <v>100000</v>
-      </c>
-      <c r="E33">
-        <v>5.8541999999999997E-2</v>
-      </c>
-    </row>
-    <row r="34" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D34">
-        <v>1000000</v>
-      </c>
-      <c r="E34">
-        <v>5.8465999999999997E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D35">
-        <v>10000000</v>
-      </c>
-      <c r="E35">
-        <v>5.8428000000000001E-2</v>
+      <c r="F36">
+        <v>67000000</v>
       </c>
     </row>
   </sheetData>
